--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.170.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.170.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.170.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.170.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:Y55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="52" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.170.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.170.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0170.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0170.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 7 â€” 8</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢t</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]163</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]163</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L3: isolated marker/symbol line :: 2</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 8</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]163</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -628,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •t</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,12 +668,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58 â€” 59</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 7â€”8</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •t</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,7 +685,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 8</t>
+          <t>L5: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -687,11 +695,15 @@
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L115: punctuation artifact: repeated periods :: Cf the Court ..</t>
+          <t>L36: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: to dissolve . . . - - - •</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 85</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -723,12 +735,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 07 â€” 108</t>
+          <t>L34: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Appearance by Guardian . . - . â€¢</t>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Appearance by Guardian . . - . •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -740,11 +752,15 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: .9</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •t</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
-      <c r="Q4" s="1" t="inlineStr"/>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>L115: punctuation artifact: repeated periods :: Cf the Court ..</t>
+        </is>
+      </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr"/>
       <c r="T4" s="1" t="inlineStr"/>
@@ -762,12 +778,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -778,12 +794,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ery 8 â€” 9</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP, U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: 。：</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: to dissolve . . . - - - â€¢</t>
+          <t>L36: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: to dissolve . . . - - - •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -795,7 +811,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 31</t>
+          <t>L25: symbol-only separator/garbage line :: . 7—8</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -831,14 +847,10 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€‚ï¼š</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Common Injunction . . â€¢ .</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Common Injunction . . • .</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -850,7 +862,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L52: symbol-only separator/garbage line :: . 31</t>
+          <t>L48: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -889,7 +901,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 54â€”55</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 85</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -901,7 +913,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 54</t>
+          <t>L49: isolated marker/symbol line :: .9</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -940,7 +952,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -56â€”57</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -952,7 +964,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 64</t>
+          <t>L51: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -991,7 +1003,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 57â€”58</t>
+          <t>L126: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1003,7 +1015,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 54</t>
+          <t>L52: symbol-only separator/garbage line :: . 31</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1025,12 +1037,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1042,7 +1054,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58â€”59</t>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1054,7 +1066,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 54</t>
+          <t>L56: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1081,7 +1093,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1093,19 +1105,19 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 85</t>
+          <t>L174: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L23: isolated marker/symbol line :: 8</t>
+          <t>L21: symbol-only separator/garbage line :: . 7 — 8</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: 64</t>
+          <t>L58: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1127,12 +1139,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1142,21 +1154,17 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Of the Master, (See Â« Masterâ€™s Office.")</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: . 9</t>
+          <t>L23: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 60</t>
+          <t>L60: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1183,7 +1191,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1193,21 +1201,17 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 31</t>
+          <t>L25: isolated marker/symbol line :: . 9</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 63</t>
+          <t>L62: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1234,7 +1238,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1244,21 +1248,17 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: 31</t>
+          <t>L27: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 58</t>
+          <t>L66: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1295,21 +1295,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L134: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 16â€”17</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 85</t>
+          <t>L29: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 61</t>
+          <t>L68: symbol-only separator/garbage line :: 54—55</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1346,21 +1342,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: 54</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 62</t>
+          <t>L70: symbol-only separator/garbage line :: -56—57</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1397,21 +1389,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: MASTERâ€™S OFFICE.</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 64</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 62</t>
+          <t>L72: symbol-only separator/garbage line :: 57—58</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1436,21 +1424,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L150: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 07â€”108</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L40: symbol-only separator/garbage line :: 5455</t>
+          <t>L34: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 62</t>
+          <t>L74: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1475,21 +1459,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L160: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ry 8â€”9</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L41: symbol-only separator/garbage line :: - 56-57</t>
+          <t>L35: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 85</t>
+          <t>L76: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1514,21 +1494,17 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L42: symbol-only separator/garbage line :: 57-58</t>
+          <t>L37: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L94: symbol-only separator/garbage line :: .84</t>
+          <t>L78: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1558,12 +1534,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 60</t>
+          <t>L39: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 84</t>
+          <t>L80: symbol-only separator/garbage line :: 58—59</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1593,12 +1569,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 63</t>
+          <t>L40: symbol-only separator/garbage line :: 5455</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L97: symbol-only separator/garbage line :: .84</t>
+          <t>L84: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1628,12 +1604,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 58</t>
+          <t>L41: symbol-only separator/garbage line :: - 56-57</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 85</t>
+          <t>L86: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1663,12 +1639,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 64</t>
+          <t>L42: symbol-only separator/garbage line :: 57-58</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 108</t>
+          <t>L88: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1698,12 +1674,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 61</t>
+          <t>L43: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L90: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1733,12 +1709,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 84</t>
+          <t>L44: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L128: symbol-only separator/garbage line :: . 107</t>
+          <t>L92: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1768,12 +1744,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: S</t>
+          <t>L45: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 7</t>
+          <t>L94: symbol-only separator/garbage line :: .84</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1803,12 +1779,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 84</t>
+          <t>L46: symbol-only separator/garbage line :: 58 — 59</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L133: symbol-only separator/garbage line :: .14</t>
+          <t>L95: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1838,12 +1814,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 84</t>
+          <t>L48: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L97: symbol-only separator/garbage line :: .84</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1873,12 +1849,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L59: isolated marker/symbol line :: 85</t>
+          <t>L49: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L152: isolated marker/symbol line :: 4</t>
+          <t>L99: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1908,12 +1884,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 85</t>
+          <t>L52: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: 9</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 85</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1943,12 +1919,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: a</t>
+          <t>L54: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L158: isolated marker/symbol line :: .8</t>
+          <t>L103: isolated marker/symbol line :: 108</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1978,12 +1954,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: 108</t>
+          <t>L55: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L159: isolated marker/symbol line :: 8</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2013,12 +1989,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 107</t>
+          <t>L57: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L164: symbol-only separator/garbage line :: .93</t>
+          <t>L126: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2048,12 +2024,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 7</t>
+          <t>L59: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L166: isolated marker/symbol line :: 93</t>
+          <t>L128: symbol-only separator/garbage line :: . 107</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2083,10 +2059,14 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 62</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr"/>
+          <t>L61: isolated marker/symbol line :: 85</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L130: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2114,10 +2094,14 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 62</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr"/>
+          <t>L62: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L133: symbol-only separator/garbage line :: .14</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2145,10 +2129,14 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 62</t>
-        </is>
-      </c>
-      <c r="O38" s="1" t="inlineStr"/>
+          <t>L64: isolated marker/symbol line :: 108</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>L134: symbol-only separator/garbage line :: 16—17</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2176,10 +2164,14 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 8</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr"/>
+          <t>L67: isolated marker/symbol line :: 107</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2207,10 +2199,14 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 8</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr"/>
+          <t>L70: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L150: symbol-only separator/garbage line :: 07—108</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2238,10 +2234,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L86: symbol-only separator/garbage line :: . 14</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L72: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L152: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2269,10 +2269,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 1.</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L73: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L154: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2300,10 +2304,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: ,</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L74: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L158: isolated marker/symbol line :: .8</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2331,10 +2339,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L90: symbol-only separator/garbage line :: 16-17</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L75: symbol-only separator/garbage line :: 07 — 108</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L159: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2362,10 +2374,14 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 9</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="inlineStr"/>
+          <t>L77: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>L164: symbol-only separator/garbage line :: .93</t>
+        </is>
+      </c>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
       <c r="R45" s="1" t="inlineStr"/>
@@ -2393,10 +2409,14 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: g</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L78: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L166: isolated marker/symbol line :: 93</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -2424,10 +2444,14 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 93</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP, U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: 。：</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L174: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -2455,7 +2479,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 93</t>
+          <t>L86: symbol-only separator/garbage line :: . 14</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2470,6 +2494,223 @@
       <c r="X48" s="1" t="inlineStr"/>
       <c r="Y48" s="1" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr"/>
+      <c r="B49" s="1" t="inlineStr"/>
+      <c r="C49" s="1" t="inlineStr"/>
+      <c r="D49" s="1" t="inlineStr"/>
+      <c r="E49" s="1" t="inlineStr"/>
+      <c r="F49" s="1" t="inlineStr"/>
+      <c r="G49" s="1" t="inlineStr"/>
+      <c r="H49" s="1" t="inlineStr"/>
+      <c r="I49" s="1" t="inlineStr"/>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
+      <c r="L49" s="1" t="inlineStr"/>
+      <c r="M49" s="1" t="inlineStr"/>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>L88: isolated marker/symbol line :: 1.</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr"/>
+      <c r="P49" s="1" t="inlineStr"/>
+      <c r="Q49" s="1" t="inlineStr"/>
+      <c r="R49" s="1" t="inlineStr"/>
+      <c r="S49" s="1" t="inlineStr"/>
+      <c r="T49" s="1" t="inlineStr"/>
+      <c r="U49" s="1" t="inlineStr"/>
+      <c r="V49" s="1" t="inlineStr"/>
+      <c r="W49" s="1" t="inlineStr"/>
+      <c r="X49" s="1" t="inlineStr"/>
+      <c r="Y49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr"/>
+      <c r="B50" s="1" t="inlineStr"/>
+      <c r="C50" s="1" t="inlineStr"/>
+      <c r="D50" s="1" t="inlineStr"/>
+      <c r="E50" s="1" t="inlineStr"/>
+      <c r="F50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr"/>
+      <c r="H50" s="1" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr"/>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
+      <c r="L50" s="1" t="inlineStr"/>
+      <c r="M50" s="1" t="inlineStr"/>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>L89: isolated marker/symbol line :: ,</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr"/>
+      <c r="P50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="inlineStr"/>
+      <c r="R50" s="1" t="inlineStr"/>
+      <c r="S50" s="1" t="inlineStr"/>
+      <c r="T50" s="1" t="inlineStr"/>
+      <c r="U50" s="1" t="inlineStr"/>
+      <c r="V50" s="1" t="inlineStr"/>
+      <c r="W50" s="1" t="inlineStr"/>
+      <c r="X50" s="1" t="inlineStr"/>
+      <c r="Y50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" s="1" t="inlineStr"/>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" s="1" t="inlineStr"/>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr"/>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
+      <c r="L51" s="1" t="inlineStr"/>
+      <c r="M51" s="1" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>L90: symbol-only separator/garbage line :: 16-17</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr"/>
+      <c r="R51" s="1" t="inlineStr"/>
+      <c r="S51" s="1" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr"/>
+      <c r="V51" s="1" t="inlineStr"/>
+      <c r="W51" s="1" t="inlineStr"/>
+      <c r="X51" s="1" t="inlineStr"/>
+      <c r="Y51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>L93: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="inlineStr"/>
+      <c r="M53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>L94: isolated marker/symbol line :: g</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr"/>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+      <c r="W53" s="1" t="inlineStr"/>
+      <c r="X53" s="1" t="inlineStr"/>
+      <c r="Y53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="1" t="inlineStr"/>
+      <c r="C54" s="1" t="inlineStr"/>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr"/>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr"/>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
+      <c r="L54" s="1" t="inlineStr"/>
+      <c r="M54" s="1" t="inlineStr"/>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>L101: isolated marker/symbol line :: 93</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr"/>
+      <c r="P54" s="1" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr"/>
+      <c r="R54" s="1" t="inlineStr"/>
+      <c r="S54" s="1" t="inlineStr"/>
+      <c r="T54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="inlineStr"/>
+      <c r="V54" s="1" t="inlineStr"/>
+      <c r="W54" s="1" t="inlineStr"/>
+      <c r="X54" s="1" t="inlineStr"/>
+      <c r="Y54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr"/>
+      <c r="B55" s="1" t="inlineStr"/>
+      <c r="C55" s="1" t="inlineStr"/>
+      <c r="D55" s="1" t="inlineStr"/>
+      <c r="E55" s="1" t="inlineStr"/>
+      <c r="F55" s="1" t="inlineStr"/>
+      <c r="G55" s="1" t="inlineStr"/>
+      <c r="H55" s="1" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr"/>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="1" t="inlineStr"/>
+      <c r="L55" s="1" t="inlineStr"/>
+      <c r="M55" s="1" t="inlineStr"/>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>L103: isolated marker/symbol line :: 93</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr"/>
+      <c r="P55" s="1" t="inlineStr"/>
+      <c r="Q55" s="1" t="inlineStr"/>
+      <c r="R55" s="1" t="inlineStr"/>
+      <c r="S55" s="1" t="inlineStr"/>
+      <c r="T55" s="1" t="inlineStr"/>
+      <c r="U55" s="1" t="inlineStr"/>
+      <c r="V55" s="1" t="inlineStr"/>
+      <c r="W55" s="1" t="inlineStr"/>
+      <c r="X55" s="1" t="inlineStr"/>
+      <c r="Y55" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
